--- a/Westergaard_Hyatt_1994/Westergaard_Hyatt_1994_registry_rows.xlsx
+++ b/Westergaard_Hyatt_1994/Westergaard_Hyatt_1994_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R0e22f7771c914ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R9ca64abe0ce046e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Reff928b08b1a43ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rf535d74366cd468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R99ad6bb9c9bb43bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rf29614f0d6714733"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Contingent action, mirror looking and inspection of otherwise invisible body regions</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Results / figures / tables: item selection pending</x:v>
+        <x:v>Figure 1: Bonobo mirror-on/off differences in behavioural frequencies</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap
@@ -350,13 +350,47 @@
         <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 2 / printed p. 274. Adjusted frequencies by age class and behavioural category; Table 1 provides subjects and Table 2 definitions. This is not a standard mark-test pass-rate dataset.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/1734575182/Westergaard-1994-The responses of bonobos (Pan.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="180" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Westergaard_Hyatt_1994</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="str">
+        <x:v>Contingent action, mirror looking and inspection of otherwise invisible body regions</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>Figure 2: Bonobo mirror-on/off differences in behavioural durations</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap
+Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued.
+Original source note: Nine bonobos; four inspected otherwise invisible body regions. This is mirror-guided self-inspection evidence, not a standard mark-test pass rate. Retain age class and behavioural categories.</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
+        <x:v>https://doi.org/10.1007/BF02435514</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>Verified in EndNote full text — PDF p. 4 / printed p. 276. Relative durations by age class and behavioural category; same study as Figure 1, distinct measurement endpoint.</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/1734575182/Westergaard-1994-The responses of bonobos (Pan.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +542,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Westergaard, G. C., &amp; Hyatt, C. W. (1994). The responses of bonobos (Pan paniscus) to their mirror images: Evidence of selfrecognition. Human Evolution, 9(4), 273–279. https://doi.org/10.1007/BF02435514</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Figure 1</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +561,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Westergaard_Hyatt_1994. Target: Results / figures / tables: item selection pending. Nine bonobos; four inspected otherwise invisible body regions. This is mirror-guided self-inspection evidence, not a standard mark-test pass rate. Retain age class and behavioural categories.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 2 / printed p. 274. Adjusted frequencies by age class and behavioural category; Table 1 provides subjects and Table 2 definitions. This is not a standard mark-test pass-rate dataset. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/1734575182/Westergaard-1994-The responses of bonobos (Pan.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
@@ -550,7 +586,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Contingent action, mirror looking and inspection of otherwise invisible body regions</x:v>
+        <x:v>Bonobo mirror-on/off differences in behavioural frequencies</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -570,6 +606,73 @@
         <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
       </x:c>
       <x:c r="AH2" s="3" t="str">
+        <x:v>Pending — no snapshot created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="200" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Westergaard, G. C., &amp; Hyatt, C. W. (1994). The responses of bonobos (Pan paniscus) to their mirror images: Evidence of selfrecognition. Human Evolution, 9(4), 273–279. https://doi.org/10.1007/BF02435514</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3" t="str">
+        <x:v>Figure 2</x:v>
+      </x:c>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="6"/>
+      <x:c r="K3" s="6"/>
+      <x:c r="L3" s="6"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="3" t="str">
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Westergaard_Hyatt_1994. Target: Results / figures / tables: item selection pending. Nine bonobos; four inspected otherwise invisible body regions. This is mirror-guided self-inspection evidence, not a standard mark-test pass rate. Retain age class and behavioural categories.
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 4 / printed p. 276. Relative durations by age class and behavioural category; same study as Figure 1, distinct measurement endpoint. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/1734575182/Westergaard-1994-The responses of bonobos (Pan.pdf</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
+      </x:c>
+      <x:c r="Q3" s="3"/>
+      <x:c r="R3" s="3" t="str">
+        <x:v>https://doi.org/10.1007/BF02435514</x:v>
+      </x:c>
+      <x:c r="S3" s="3"/>
+      <x:c r="T3" s="3" t="str">
+        <x:v>Nine bonobos; four inspected otherwise invisible body regions. This is mirror-guided self-inspection evidence, not a standard mark-test pass rate. Retain age class and behavioural categories.</x:v>
+      </x:c>
+      <x:c r="U3" s="3"/>
+      <x:c r="V3" s="3" t="str">
+        <x:v>Mirror recognition</x:v>
+      </x:c>
+      <x:c r="W3" s="3" t="str">
+        <x:v>Primates</x:v>
+      </x:c>
+      <x:c r="X3" s="3" t="str">
+        <x:v>Bonobo mirror-on/off differences in behavioural durations</x:v>
+      </x:c>
+      <x:c r="Y3" s="3"/>
+      <x:c r="Z3" s="3"/>
+      <x:c r="AA3" s="3" t="str">
+        <x:v>Alternating reflective and non-reflective mirror surfaces</x:v>
+      </x:c>
+      <x:c r="AB3" s="3" t="str">
+        <x:v>Behavioural observation (retain endpoint, individual and condition)</x:v>
+      </x:c>
+      <x:c r="AC3" s="3"/>
+      <x:c r="AD3" s="3"/>
+      <x:c r="AE3" s="3" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+      <x:c r="AF3" s="3"/>
+      <x:c r="AG3" s="3" t="str">
+        <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
+      </x:c>
+      <x:c r="AH3" s="3" t="str">
         <x:v>Pending — no snapshot created</x:v>
       </x:c>
     </x:row>
@@ -703,7 +806,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="100" customHeight="1">
@@ -711,7 +814,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -995,13 +1098,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62090DC8-7B2B-4673-AF47-84D9499DECD8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A14592-E2C3-42A1-8585-47B32B49A0CB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{558594EB-38F1-4A12-9632-E838452E3677}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{381F9409-4E65-4CE6-B63A-8FA73662CB6E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D2C214-F447-4A21-B323-1662755D2358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEF19AC5-B0A2-4EB6-B185-707D330103A4}"/>
 </file>